--- a/public/docs/FATCA_Schema 2.0.xlsx
+++ b/public/docs/FATCA_Schema 2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Python-Hub\GithubRepos\mft1998-portfolio\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Python-Hub\GithubRepos\XML-Schema-viewer\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C0F2BF-B4C7-4902-ACE7-51DB45C7D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810D3555-F359-41F0-907B-B097D5635E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{18F53C85-61FE-4B9A-B576-452BD9DB7FDE}"/>
+    <workbookView xWindow="0" yWindow="4215" windowWidth="13785" windowHeight="11385" xr2:uid="{18F53C85-61FE-4B9A-B576-452BD9DB7FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="125">
   <si>
     <t>tag_id</t>
   </si>
@@ -303,9 +303,6 @@
   </si>
   <si>
     <t>Organization</t>
-  </si>
-  <si>
-    <t>AccountHolder Type</t>
   </si>
   <si>
     <t>C</t>
@@ -382,6 +379,39 @@
   </si>
   <si>
     <t>is_notNew</t>
+  </si>
+  <si>
+    <t>unique ID of the previously sent Account report</t>
+  </si>
+  <si>
+    <t>unique ID of the previously sent Document</t>
+  </si>
+  <si>
+    <t>unique ID of the previously sent Message</t>
+  </si>
+  <si>
+    <t>unique ID of the previously sent Account Report</t>
+  </si>
+  <si>
+    <t>Individual Owner</t>
+  </si>
+  <si>
+    <t>Organization Owner</t>
+  </si>
+  <si>
+    <t>SSN or ITIN</t>
+  </si>
+  <si>
+    <t>123456789 or 123-45-6789 or 12-3456789</t>
+  </si>
+  <si>
+    <t>AccountHolderType</t>
+  </si>
+  <si>
+    <t>mandatory if AccountHolder is Organization &amp; AccountHolderType is FATCA 101 or 102</t>
+  </si>
+  <si>
+    <t>Contain Data on the Organization's Owner</t>
   </si>
 </sst>
 </file>
@@ -759,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C42EF740-40BD-4580-AA1E-7E614CAA4224}">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
@@ -815,7 +845,7 @@
         <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -1363,7 +1393,7 @@
         <v>70</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -1385,6 +1415,9 @@
       <c r="G30" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H30" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M30">
         <v>1</v>
       </c>
@@ -1457,7 +1490,7 @@
         <v>70</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -1479,6 +1512,9 @@
       <c r="G35" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H35" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="M35">
         <v>1</v>
       </c>
@@ -1568,7 +1604,7 @@
         <v>70</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="M40">
         <v>1</v>
@@ -1590,6 +1626,9 @@
       <c r="G41" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H41" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="M41">
         <v>1</v>
       </c>
@@ -1656,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1667,7 +1706,13 @@
         <v>15</v>
       </c>
       <c r="F46" s="1">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -1684,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -1704,7 +1749,7 @@
         <v>2</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -1752,7 +1797,7 @@
         <v>65</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -1769,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>65</v>
@@ -1783,7 +1828,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1">
         <v>44</v>
@@ -1792,13 +1837,13 @@
         <v>3</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="J53" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>65</v>
@@ -1812,7 +1857,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C54" s="1">
         <v>46</v>
@@ -1824,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -1847,7 +1892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1860,14 +1905,11 @@
       <c r="F56" s="1">
         <v>3</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H56" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -1875,7 +1917,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C57" s="1">
         <v>55</v>
@@ -1923,7 +1965,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C60" s="1">
         <v>50</v>
@@ -1937,7 +1979,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C61" s="1">
         <v>50</v>
@@ -1951,7 +1993,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C62" s="1">
         <v>47</v>
@@ -1960,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -1968,7 +2010,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C63" s="1">
         <v>47</v>
@@ -1977,7 +2019,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -1985,7 +2027,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C64" s="1">
         <v>47</v>
@@ -1994,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -2002,7 +2044,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" s="1">
         <v>63</v>
@@ -2014,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -2107,6 +2149,9 @@
       <c r="G70" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H70" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="M70">
         <v>1</v>
       </c>
@@ -2116,7 +2161,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C71" s="1">
         <v>16</v>
@@ -2125,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -2136,7 +2181,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C72" s="1">
         <v>16</v>
@@ -2145,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -2156,7 +2201,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C73" s="1">
         <v>16</v>
@@ -2165,10 +2210,10 @@
         <v>1</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -2176,7 +2221,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" s="1">
         <v>72</v>
@@ -2188,15 +2233,358 @@
         <v>1</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
+      <c r="B75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="1">
+        <v>45</v>
+      </c>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L75" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" s="1">
+        <v>45</v>
+      </c>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L76" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="1">
+        <v>74</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="1">
+        <v>74</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" s="1">
+        <v>77</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>2</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="1">
+        <v>74</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="1">
+        <v>74</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" s="1">
+        <v>74</v>
+      </c>
+      <c r="F82" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" s="1">
+        <v>74</v>
+      </c>
+      <c r="F83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" s="1">
+        <v>75</v>
+      </c>
+      <c r="F84" s="4">
+        <v>2</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="1">
+        <v>75</v>
+      </c>
+      <c r="F85" s="1">
+        <v>3</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="1">
+        <v>84</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>2</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="1">
+        <v>75</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88" s="1">
+        <v>75</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" s="1">
+        <v>51</v>
+      </c>
+      <c r="F89" s="4">
+        <v>2</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C90" s="1">
+        <v>51</v>
+      </c>
+      <c r="F90" s="1">
+        <v>3</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="1">
+        <v>89</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4">
+        <v>2</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C92" s="1">
+        <v>51</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C93" s="1">
+        <v>51</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>